--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimen\OneDrive\Escritorio\Proyecto-Nuva-Oxi\1 venta sell in\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68BDD533-0E95-4489-8301-68B9619761DF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="ANALISIS" sheetId="6" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="DatosExternos_1" localSheetId="2">ref_SKU!$A$1:$F$7</definedName>
     <definedName name="DatosExternos_1" localSheetId="4">VENTAS!$A$1:$L$7</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -434,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -443,11 +443,21 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -472,15 +482,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -546,17 +547,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BA14279-21ED-476D-8ADB-89B1E1EFEBD1}" name="tblPedidosSI" displayName="tblPedidosSI" ref="A1:M4" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BA14279-21ED-476D-8ADB-89B1E1EFEBD1}" name="tblPedidosSI" displayName="tblPedidosSI" ref="A1:M4" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A1:M4" xr:uid="{3BA14279-21ED-476D-8ADB-89B1E1EFEBD1}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{3A007A5C-2B0C-4021-B913-2CB602DD85FE}" name="ID_Pedido"/>
     <tableColumn id="2" xr3:uid="{20B450C2-00CF-402E-9F8A-BF7F9800E723}" name="ID_Cliente"/>
-    <tableColumn id="3" xr3:uid="{F162E49B-EBF5-4470-9B61-3FC090AFFF55}" name="Fecha_OC" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F162E49B-EBF5-4470-9B61-3FC090AFFF55}" name="Fecha_OC" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{219F1893-77C4-40D0-A30F-A7C14F23AFF7}" name="N_OC"/>
     <tableColumn id="5" xr3:uid="{35F2501B-1F67-4A70-8749-0D2CE4328C1B}" name="Monto_OC"/>
-    <tableColumn id="6" xr3:uid="{263F3E60-2DFA-456B-A9B4-356D717B4B06}" name="Fecha_Despacho" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{263F3E60-2DFA-456B-A9B4-356D717B4B06}" name="Fecha_Despacho" dataDxfId="1"/>
     <tableColumn id="7" xr3:uid="{A2C6BD83-105C-4325-AC80-C6E7D44A2925}" name="N_Guia"/>
-    <tableColumn id="8" xr3:uid="{FDD1F0F3-9BD1-47EA-9A0C-F7564F93582B}" name="Fecha_Factura" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{FDD1F0F3-9BD1-47EA-9A0C-F7564F93582B}" name="Fecha_Factura" dataDxfId="0"/>
     <tableColumn id="9" xr3:uid="{65D18860-823E-4C8B-AA69-B8822DCE4B05}" name="N_Factura"/>
     <tableColumn id="10" xr3:uid="{2466B7DD-4732-4EC2-958D-70BB92DF14CE}" name="Estado"/>
     <tableColumn id="11" xr3:uid="{D7DBEAA5-7731-4F6C-A163-D8FA6FC79157}" name="Fecha_Pago_Real"/>
@@ -1087,7 +1088,7 @@
       </c>
       <c r="L2">
         <f ca="1">IF(K2="",TODAY()-C2,K2-C2)</f>
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M2" t="s">
         <v>84</v>
@@ -1499,7 +1500,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
@@ -1553,7 +1554,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="6">
         <v>46027</v>
       </c>
       <c r="C2" t="s">
@@ -1583,7 +1584,7 @@
       <c r="K2">
         <v>46057</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="6">
         <v>46057</v>
       </c>
     </row>
@@ -1591,7 +1592,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="6">
         <v>46028</v>
       </c>
       <c r="C3" t="s">
@@ -1621,7 +1622,7 @@
       <c r="K3">
         <v>46058</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="6">
         <v>46058</v>
       </c>
     </row>
@@ -1629,7 +1630,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="6">
         <v>46029</v>
       </c>
       <c r="C4" t="s">
@@ -1659,12 +1660,13 @@
       <c r="K4">
         <v>46059</v>
       </c>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="6">
         <v>46031</v>
       </c>
       <c r="C5" t="s">
@@ -1694,7 +1696,7 @@
       <c r="K5">
         <v>46061</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="6">
         <v>46061</v>
       </c>
     </row>
@@ -1702,7 +1704,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="6">
         <v>46034</v>
       </c>
       <c r="C6" t="s">
@@ -1737,7 +1739,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="6">
         <v>46035</v>
       </c>
       <c r="C7" t="s">

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68BDD533-0E95-4489-8301-68B9619761DF}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4F7EADE-5832-427F-8A6E-0859B2FD1E3F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>Venta por Cliente</t>
+  </si>
+  <si>
+    <t>precio cotizacion</t>
   </si>
 </sst>
 </file>
@@ -1496,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D91C53-D7D2-42B7-8F5B-EDC2F2628FCD}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
@@ -1512,7 +1515,7 @@
     <col min="12" max="12" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1549,8 +1552,11 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1588,7 +1594,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1626,7 +1632,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1662,7 +1668,7 @@
       </c>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1700,7 +1706,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1735,7 +1741,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4F7EADE-5832-427F-8A6E-0859B2FD1E3F}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2705EDC9-899F-4333-9F83-9769E5EC6B55}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="ANALISIS" sheetId="6" r:id="rId1"/>
@@ -232,24 +232,15 @@
     <t>Costo_Unit</t>
   </si>
   <si>
-    <t>Barra Cacao 40g</t>
-  </si>
-  <si>
     <t>Cacao</t>
   </si>
   <si>
     <t>Unitaria</t>
   </si>
   <si>
-    <t>Barra Mani 40g</t>
-  </si>
-  <si>
     <t>Mani</t>
   </si>
   <si>
-    <t>Barra Frutal 40g</t>
-  </si>
-  <si>
     <t>Frutal</t>
   </si>
   <si>
@@ -368,6 +359,15 @@
   </si>
   <si>
     <t>precio cotizacion</t>
+  </si>
+  <si>
+    <t>Barra Cacao 35g</t>
+  </si>
+  <si>
+    <t>Barra Mani 35g</t>
+  </si>
+  <si>
+    <t>Barra Frutal 35g</t>
   </si>
 </sst>
 </file>
@@ -899,12 +899,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B3" s="5">
         <f>SUM(VENTAS!F:F)</f>
@@ -913,7 +913,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" s="5">
         <f>SUM(VENTAS!G:G)</f>
@@ -922,7 +922,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B5" s="5">
         <f>SUM(VENTAS!I:I)</f>
@@ -931,7 +931,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B6" s="5">
         <f>SUMIF(VENTAS!J:J,"Emitida",VENTAS!G:G)</f>
@@ -943,7 +943,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B8" s="5"/>
     </row>
@@ -1019,48 +1019,48 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -1069,7 +1069,7 @@
         <v>46032</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E2">
         <v>295000</v>
@@ -1078,28 +1078,28 @@
         <v>46034</v>
       </c>
       <c r="G2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H2" s="3">
         <v>46035</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L2">
         <f ca="1">IF(K2="",TODAY()-C2,K2-C2)</f>
         <v>179</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -1108,7 +1108,7 @@
         <v>46033</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E3">
         <v>47200</v>
@@ -1117,16 +1117,16 @@
         <v>46034</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H3" s="3">
         <v>46034</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K3" s="3">
         <v>46037</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1150,7 +1150,7 @@
         <v>46027</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E4">
         <v>22800</v>
@@ -1159,16 +1159,16 @@
         <v>46027</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3">
         <v>46027</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K4" s="3">
         <v>46027</v>
@@ -1224,13 +1224,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
       </c>
       <c r="E2">
         <v>1596.6386554621847</v>
@@ -1244,13 +1244,13 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>1596.6386554621847</v>
@@ -1264,13 +1264,13 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>1596.6386554621847</v>
@@ -1284,13 +1284,13 @@
         <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E5">
         <v>4957.9831932773113</v>
@@ -1304,13 +1304,13 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E6">
         <v>4957.9831932773113</v>
@@ -1324,13 +1324,13 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E7">
         <v>4957.9831932773113</v>
@@ -1553,7 +1553,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2705EDC9-899F-4333-9F83-9769E5EC6B55}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D00D1FA9-BE4C-4F51-A9FD-AF2BEA3B5E72}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="ANALISIS" sheetId="6" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="104">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -368,6 +368,12 @@
   </si>
   <si>
     <t>Barra Frutal 35g</t>
+  </si>
+  <si>
+    <t>revisar</t>
+  </si>
+  <si>
+    <t>Form</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E712B3CB-4D88-4B27-895C-0C806C7E03D9}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
@@ -1337,6 +1343,11 @@
       </c>
       <c r="F7">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1499,7 +1510,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D91C53-D7D2-42B7-8F5B-EDC2F2628FCD}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
@@ -1776,6 +1787,11 @@
         <v>46065</v>
       </c>
     </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D00D1FA9-BE4C-4F51-A9FD-AF2BEA3B5E72}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{984928DF-3C16-42C7-8E13-C1BD4426E7EC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
+    <workbookView minimized="1" xWindow="4150" yWindow="1560" windowWidth="14400" windowHeight="7280" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="ANALISIS" sheetId="6" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -373,7 +373,10 @@
     <t>revisar</t>
   </si>
   <si>
-    <t>Form</t>
+    <t>Vista equipo</t>
+  </si>
+  <si>
+    <t>agregar form</t>
   </si>
 </sst>
 </file>
@@ -1510,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D91C53-D7D2-42B7-8F5B-EDC2F2628FCD}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
@@ -1792,6 +1795,11 @@
         <v>103</v>
       </c>
     </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{43F4BD09-D69D-4734-82C6-EF96A263399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{984928DF-3C16-42C7-8E13-C1BD4426E7EC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4150" yWindow="1560" windowWidth="14400" windowHeight="7280" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="ANALISIS" sheetId="6" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="DatosExternos_1" localSheetId="2">ref_SKU!$A$1:$F$7</definedName>
     <definedName name="DatosExternos_1" localSheetId="4">VENTAS!$A$1:$L$7</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A692D81-525B-40F4-A249-0AC4BAA3340A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="DatosExternos_1" localSheetId="2">ref_SKU!$A$1:$F$7</definedName>
     <definedName name="DatosExternos_1" localSheetId="4">VENTAS!$A$1:$L$7</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="106">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>agregar form</t>
+  </si>
+  <si>
+    <t>dejar en uno solo</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{381EA1F5-A53B-4A26-9C3F-8085720778A8}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" customWidth="1"/>
@@ -1185,6 +1188,11 @@
       <c r="L4">
         <f ca="1">IF(K4="",TODAY()-C4,K4-C4)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A692D81-525B-40F4-A249-0AC4BAA3340A}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63832B9B-FECD-4C3A-9DA2-13363FF3DEFA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="ANALISIS" sheetId="6" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="117">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -380,6 +380,39 @@
   </si>
   <si>
     <t>dejar en uno solo</t>
+  </si>
+  <si>
+    <t>Cobertura</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>j</t>
   </si>
 </sst>
 </file>
@@ -1521,7 +1554,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D91C53-D7D2-42B7-8F5B-EDC2F2628FCD}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
@@ -1808,6 +1841,91 @@
         <v>104</v>
       </c>
     </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63832B9B-FECD-4C3A-9DA2-13363FF3DEFA}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36459D6F-1706-4DAC-B5FD-F53E1D1D5AFA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="122">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -413,6 +413,21 @@
   </si>
   <si>
     <t>j</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>pendiente</t>
+  </si>
+  <si>
+    <t>semana 1</t>
+  </si>
+  <si>
+    <t>resultado</t>
   </si>
 </sst>
 </file>
@@ -482,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -492,6 +507,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,7 +969,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM(VENTAS!F:F)</f>
-        <v>92</v>
+        <v>46396</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1562,7 +1578,7 @@
     <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.90625" bestFit="1" customWidth="1"/>
@@ -1845,6 +1861,15 @@
       <c r="A13" t="s">
         <v>106</v>
       </c>
+      <c r="C13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F13" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -1853,6 +1878,12 @@
       <c r="B14" t="s">
         <v>107</v>
       </c>
+      <c r="D14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="7">
+        <v>46304</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -1861,6 +1892,9 @@
       <c r="B15" t="s">
         <v>108</v>
       </c>
+      <c r="D15" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
@@ -1868,6 +1902,9 @@
       </c>
       <c r="B16" t="s">
         <v>109</v>
+      </c>
+      <c r="D16" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36459D6F-1706-4DAC-B5FD-F53E1D1D5AFA}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1225F994-A872-413C-8779-10701E883F31}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="127">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -428,6 +428,21 @@
   </si>
   <si>
     <t>resultado</t>
+  </si>
+  <si>
+    <t>plan de ejecucion</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>restriccion</t>
+  </si>
+  <si>
+    <t>semanal</t>
+  </si>
+  <si>
+    <t>Obligatorio 1</t>
   </si>
 </sst>
 </file>
@@ -1857,6 +1872,14 @@
         <v>104</v>
       </c>
     </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
+      </c>
+    </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>106</v>
@@ -1867,8 +1890,14 @@
       <c r="D13" t="s">
         <v>120</v>
       </c>
+      <c r="E13" t="s">
+        <v>125</v>
+      </c>
       <c r="F13" t="s">
         <v>121</v>
+      </c>
+      <c r="H13" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -1880,6 +1909,9 @@
       </c>
       <c r="D14" t="s">
         <v>118</v>
+      </c>
+      <c r="E14" t="s">
+        <v>126</v>
       </c>
       <c r="F14" s="7">
         <v>46304</v>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1225F994-A872-413C-8779-10701E883F31}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3C97F1F-072B-49A4-94EF-FD10084CF7C6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="123">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -385,9 +385,6 @@
     <t>Cobertura</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
     <t>b</t>
   </si>
   <si>
@@ -415,34 +412,25 @@
     <t>j</t>
   </si>
   <si>
-    <t>Julio</t>
-  </si>
-  <si>
     <t>ok</t>
   </si>
   <si>
     <t>pendiente</t>
   </si>
   <si>
-    <t>semana 1</t>
-  </si>
-  <si>
     <t>resultado</t>
   </si>
   <si>
     <t>plan de ejecucion</t>
   </si>
   <si>
-    <t>variable</t>
-  </si>
-  <si>
-    <t>restriccion</t>
-  </si>
-  <si>
     <t>semanal</t>
   </si>
   <si>
-    <t>Obligatorio 1</t>
+    <t>Aldea Nativa</t>
+  </si>
+  <si>
+    <t>Periodicidad</t>
   </si>
 </sst>
 </file>
@@ -1592,7 +1580,7 @@
     <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -1872,32 +1860,18 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" t="s">
-        <v>124</v>
-      </c>
-    </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -1905,13 +1879,13 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>121</v>
+      </c>
+      <c r="C14" t="s">
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F14" s="7">
         <v>46304</v>
@@ -1922,10 +1896,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>107</v>
+      </c>
+      <c r="C15" t="s">
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -1933,66 +1910,90 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="C16" t="s">
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+      <c r="C18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="C22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>115</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3C97F1F-072B-49A4-94EF-FD10084CF7C6}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3253F8AF-4739-4CF7-B8FC-27364BD46107}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="124">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -412,15 +412,6 @@
     <t>j</t>
   </si>
   <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>pendiente</t>
-  </si>
-  <si>
-    <t>resultado</t>
-  </si>
-  <si>
     <t>plan de ejecucion</t>
   </si>
   <si>
@@ -431,6 +422,18 @@
   </si>
   <si>
     <t>Periodicidad</t>
+  </si>
+  <si>
+    <t>Mensual</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>no visitado</t>
+  </si>
+  <si>
+    <t>Plan</t>
   </si>
 </sst>
 </file>
@@ -972,7 +975,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM(VENTAS!F:F)</f>
-        <v>46396</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1578,7 +1581,7 @@
   <cols>
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.08984375" bestFit="1" customWidth="1"/>
@@ -1865,13 +1868,16 @@
         <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>119</v>
+      </c>
+      <c r="D13" t="s">
+        <v>121</v>
       </c>
       <c r="F13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -1879,17 +1885,15 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F14" s="7">
-        <v>46304</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -1899,10 +1903,10 @@
         <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -1916,10 +1920,10 @@
         <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1</v>
       </c>
@@ -1927,10 +1931,13 @@
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="D17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1938,10 +1945,13 @@
         <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1</v>
       </c>
@@ -1949,10 +1959,13 @@
         <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="D19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1</v>
       </c>
@@ -1960,10 +1973,13 @@
         <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1</v>
       </c>
@@ -1971,10 +1987,13 @@
         <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1</v>
       </c>
@@ -1982,10 +2001,13 @@
         <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="D22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1</v>
       </c>
@@ -1993,7 +2015,10 @@
         <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3253F8AF-4739-4CF7-B8FC-27364BD46107}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75E3DDAB-C877-409A-B29A-5D22FB45AC25}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="123">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -431,9 +431,6 @@
   </si>
   <si>
     <t>no visitado</t>
-  </si>
-  <si>
-    <t>Plan</t>
   </si>
 </sst>
 </file>
@@ -1582,7 +1579,7 @@
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.36328125" bestFit="1" customWidth="1"/>
@@ -1873,8 +1870,8 @@
       <c r="D13" t="s">
         <v>121</v>
       </c>
-      <c r="F13" t="s">
-        <v>123</v>
+      <c r="E13" t="s">
+        <v>106</v>
       </c>
       <c r="H13" t="s">
         <v>116</v>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75E3DDAB-C877-409A-B29A-5D22FB45AC25}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95302D2C-3116-4951-84AC-E19BFED6FE03}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
@@ -1573,7 +1573,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D91C53-D7D2-42B7-8F5B-EDC2F2628FCD}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
@@ -2018,6 +2018,11 @@
         <v>122</v>
       </c>
     </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95302D2C-3116-4951-84AC-E19BFED6FE03}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F01B80E7-858A-494A-B9AA-0D4ABF489BE5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="124">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -431,6 +431,9 @@
   </si>
   <si>
     <t>no visitado</t>
+  </si>
+  <si>
+    <t>ver zona</t>
   </si>
 </sst>
 </file>
@@ -1876,6 +1879,9 @@
       <c r="H13" t="s">
         <v>116</v>
       </c>
+      <c r="J13" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">

--- a/1 venta sell in/BD_SELL_IN_NUVA.xlsx
+++ b/1 venta sell in/BD_SELL_IN_NUVA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/Proyecto-Nuva-Oxi/1 venta sell in/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/jose_vidal_conchaytoro_cl/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="14_{2093FD1B-1272-4C46-A2D8-8D2742D38FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F01B80E7-858A-494A-B9AA-0D4ABF489BE5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B98CD5A-773B-4EBE-A0B8-89E5CDB14841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
+    <workbookView xWindow="28680" yWindow="2175" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{A457DA66-1803-4DEC-82CE-ADDD8E755DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="ANALISIS" sheetId="6" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="DatosExternos_1" localSheetId="2">ref_SKU!$A$1:$F$7</definedName>
     <definedName name="DatosExternos_1" localSheetId="4">VENTAS!$A$1:$L$7</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM(VENTAS!F:F)</f>
-        <v>92</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="L2">
         <f ca="1">IF(K2="",TODAY()-C2,K2-C2)</f>
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M2" t="s">
         <v>81</v>
@@ -1650,7 +1650,7 @@
         <v>14</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="G2">
         <v>19160</v>
